--- a/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.18%1,001,000</t>
+          <t>7.21%871,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.18%</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1001000</v>
+        <v>871000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1215</v>
+        <v>1305</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.95%2,482,000</t>
+          <t>7.11%2,482,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.82%1,161,000</t>
+          <t>7.00%1,161,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.82%</t>
+          <t>7.00%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.64%1,116,000</t>
+          <t>6.61%1,116,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.64%</t>
+          <t>6.61%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1565</v>
+        <v>1510</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.21%1,630,000</t>
+          <t>6.02%1,630,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.21%</t>
+          <t>6.02%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.97%205,000</t>
+          <t>5.72%205,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.97%</t>
+          <t>5.72%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.50%465,000</t>
+          <t>5.46%465,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1900</v>
+        <v>1965</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.80%1,104,000</t>
+          <t>4.95%1,104,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>4.95%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,25 +992,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.85%5030</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5030</v>
+        <v>6290</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.29%344,000</t>
+          <t>4.29%293,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>344000</v>
+        <v>293000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>-1.85%5030</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6205</v>
+        <v>5030</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.24%293,000</t>
+          <t>4.08%344,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.08%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>293000</v>
+        <v>344000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.25%190.5</t>
+          <t>-2.1%186.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.23%7,245,000</t>
+          <t>3.26%7,245,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%116</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>116</v>
+        <v>1460</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.18%11,420,868</t>
+          <t>3.24%968,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>11420868</v>
+        <v>968000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>+9.94%553</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7900</v>
+        <v>553</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.12%164,000</t>
+          <t>3.18%2,682,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>164000</v>
+        <v>2682000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.5%503</t>
+          <t>0%116</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>503</v>
+        <v>116</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.09%2,682,000</t>
+          <t>3.13%11,420,868</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2682000</v>
+        <v>11420868</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:18</t>
+          <t>2026-10-02 19:05:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1420</v>
+        <v>7900</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.96%968,000</t>
+          <t>3.06%164,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>968000</v>
+        <v>164000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.89%2,213,000</t>
+          <t>2.77%2,213,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.09%546</t>
+          <t>+6.23%580</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>+6.23%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.22%1,700,000</t>
+          <t>2.19%1,700,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2110</v>
+        <v>260</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.17%429,675</t>
+          <t>2.18%3,645,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>429675</v>
+        <v>3645000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>254</v>
+        <v>2085</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.16%3,645,000</t>
+          <t>2.14%429,675</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3645000</v>
+        <v>429675</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.11%179,000</t>
+          <t>2.10%179,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.10%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.12%1010</t>
+          <t>+3.96%1050</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+3.96%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1010</v>
+        <v>1050</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.94%844,013</t>
+          <t>2.01%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.59%510</t>
+          <t>+10%561</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.88%200,000</t>
+          <t>0.90%200,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.7%5770</t>
+          <t>+5.2%6070</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>+5.2%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5770</v>
+        <v>6070</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.70%51,000</t>
+          <t>0.69%51,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.05%642</t>
+          <t>+6.39%683</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+6.39%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>642</v>
+        <v>683</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.55%33,000</t>
+          <t>0.54%33,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.55%19040</t>
+          <t>+9.96%127</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>19040</v>
+        <v>127</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.51%11,000</t>
+          <t>0.53%1,957,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>11000</v>
+        <v>1957000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+7.71%852</t>
+          <t>-2%835</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+7.71%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>852</v>
+        <v>835</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.50%261,000</t>
+          <t>0.52%261,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.87%115.5</t>
+          <t>+1.55%19040</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>115.5</v>
+        <v>19040</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.49%1,957,000</t>
+          <t>0.49%11,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1957000</v>
+        <v>11000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:19</t>
+          <t>2026-10-02 19:05:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.16%1305</t>
+          <t>-1.53%1285</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1305</v>
+        <v>1285</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.45%155,000</t>
+          <t>0.48%155,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.42%965</t>
+          <t>+2.11%775</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>965</v>
+        <v>775</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.45%196,000</t>
+          <t>0.45%250,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>196000</v>
+        <v>250000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.79%284.5</t>
+          <t>-0.31%962</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>284.5</v>
+        <v>962</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.45%659,000</t>
+          <t>0.45%196,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>659000</v>
+        <v>196000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.79%368.5</t>
+          <t>-1.05%281.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>368.5</v>
+        <v>281.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.44%508,000</t>
+          <t>0.44%659,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>508000</v>
+        <v>659000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.4%759</t>
+          <t>+1.36%373.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>759</v>
+        <v>373.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.44%250,000</t>
+          <t>0.44%508,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>250000</v>
+        <v>508000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.67%1275</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1275</v>
+        <v>713</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.42%134,000</t>
+          <t>0.42%250,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>134000</v>
+        <v>250000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.99%1535</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>710</v>
+        <v>1535</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.41%250,000</t>
+          <t>0.41%113,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>250000</v>
+        <v>113000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.99%1535</t>
+          <t>-2.67%1275</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1535</v>
+        <v>1275</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.40%113,000</t>
+          <t>0.40%134,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>113000</v>
+        <v>134000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2080</v>
+        <v>2190</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.40%76,000</t>
+          <t>0.37%76,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.31%99,952</t>
+          <t>0.30%99,952</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:21</t>
+          <t>2026-10-02 19:05:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:53</t>
+          <t>2026-10-02 22:50:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:54</t>
+          <t>2026-10-02 22:50:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:56</t>
+          <t>2026-10-02 22:50:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:20</t>
+          <t>2026-10-02 22:59:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:21</t>
+          <t>2026-10-02 22:59:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:50:23</t>
+          <t>2026-10-02 22:59:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:00</t>
+          <t>2026-10-02 23:48:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:01</t>
+          <t>2026-10-02 23:48:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:59:03</t>
+          <t>2026-10-02 23:48:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
